--- a/data/新建 Microsoft Excel 工作表.xlsx
+++ b/data/新建 Microsoft Excel 工作表.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\2025\2025 leybold 图论\lbgraph\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEB6F3C-28DC-485A-BCB7-75B30F89551C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1276F4D7-E407-45C0-B780-BD513535B45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11020" yWindow="1900" windowWidth="20980" windowHeight="9320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10600" yWindow="1240" windowWidth="20980" windowHeight="9320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="未完成" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2544" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="203">
   <si>
     <t>EDB</t>
   </si>
@@ -653,6 +654,14 @@
   </si>
   <si>
     <t>FLK-D25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -708,14 +717,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1630,6 +1637,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>202</v>
+      </c>
       <c r="E1" t="s">
         <v>155</v>
       </c>
@@ -3180,7 +3193,7 @@
       <c r="E92" t="s">
         <v>199</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92">
         <v>35</v>
       </c>
     </row>
@@ -3197,7 +3210,7 @@
       <c r="E93" t="s">
         <v>199</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93">
         <v>35</v>
       </c>
     </row>
@@ -3214,7 +3227,7 @@
       <c r="E94" t="s">
         <v>199</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94">
         <v>35</v>
       </c>
     </row>
@@ -3231,7 +3244,7 @@
       <c r="E95" t="s">
         <v>199</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95">
         <v>35</v>
       </c>
     </row>
@@ -3248,7 +3261,7 @@
       <c r="E96" t="s">
         <v>199</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96">
         <v>35</v>
       </c>
     </row>
@@ -3265,7 +3278,7 @@
       <c r="E97" t="s">
         <v>199</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97">
         <v>35</v>
       </c>
     </row>
@@ -3282,7 +3295,7 @@
       <c r="E98" t="s">
         <v>199</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98">
         <v>35</v>
       </c>
     </row>
@@ -3299,7 +3312,7 @@
       <c r="E99" t="s">
         <v>199</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99">
         <v>35</v>
       </c>
     </row>
@@ -3316,7 +3329,7 @@
       <c r="E100" t="s">
         <v>200</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100">
         <v>35</v>
       </c>
     </row>
@@ -3333,7 +3346,7 @@
       <c r="E101" t="s">
         <v>199</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101">
         <v>35</v>
       </c>
     </row>
@@ -3350,7 +3363,7 @@
       <c r="E102" t="s">
         <v>199</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102">
         <v>35</v>
       </c>
     </row>
@@ -3367,7 +3380,7 @@
       <c r="E103" t="s">
         <v>199</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103">
         <v>35</v>
       </c>
     </row>
@@ -3384,7 +3397,7 @@
       <c r="E104" t="s">
         <v>199</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104">
         <v>35</v>
       </c>
     </row>
@@ -3401,7 +3414,7 @@
       <c r="E105" t="s">
         <v>199</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105">
         <v>35</v>
       </c>
     </row>
@@ -3418,7 +3431,7 @@
       <c r="E106" t="s">
         <v>199</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106">
         <v>35</v>
       </c>
     </row>
@@ -3435,7 +3448,7 @@
       <c r="E107" t="s">
         <v>199</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107">
         <v>35</v>
       </c>
     </row>
@@ -3452,7 +3465,7 @@
       <c r="E108" t="s">
         <v>199</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108">
         <v>35</v>
       </c>
     </row>
@@ -3469,7 +3482,7 @@
       <c r="E109" t="s">
         <v>199</v>
       </c>
-      <c r="F109" s="5">
+      <c r="F109">
         <v>35</v>
       </c>
     </row>
@@ -3486,7 +3499,7 @@
       <c r="E110" t="s">
         <v>199</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110">
         <v>35</v>
       </c>
     </row>
@@ -3503,7 +3516,7 @@
       <c r="E111" t="s">
         <v>199</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111">
         <v>35</v>
       </c>
     </row>
@@ -3520,7 +3533,7 @@
       <c r="E112" t="s">
         <v>199</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112">
         <v>35</v>
       </c>
     </row>
@@ -3537,7 +3550,7 @@
       <c r="E113" t="s">
         <v>199</v>
       </c>
-      <c r="F113" s="5">
+      <c r="F113">
         <v>35</v>
       </c>
     </row>
@@ -3554,7 +3567,7 @@
       <c r="E114" t="s">
         <v>199</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114">
         <v>35</v>
       </c>
     </row>
@@ -3571,7 +3584,7 @@
       <c r="E115" t="s">
         <v>199</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115">
         <v>35</v>
       </c>
     </row>
@@ -3588,7 +3601,7 @@
       <c r="E116" t="s">
         <v>199</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116">
         <v>35</v>
       </c>
     </row>
@@ -3605,7 +3618,7 @@
       <c r="E117" t="s">
         <v>199</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117">
         <v>35</v>
       </c>
     </row>
@@ -3622,7 +3635,7 @@
       <c r="E118" t="s">
         <v>199</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118">
         <v>35</v>
       </c>
     </row>
@@ -3639,7 +3652,7 @@
       <c r="E119" t="s">
         <v>199</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119">
         <v>35</v>
       </c>
     </row>
@@ -3656,7 +3669,7 @@
       <c r="E120" t="s">
         <v>199</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120">
         <v>35</v>
       </c>
     </row>
@@ -3673,7 +3686,7 @@
       <c r="E121" t="s">
         <v>199</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121">
         <v>35</v>
       </c>
     </row>
@@ -3690,7 +3703,7 @@
       <c r="E122" t="s">
         <v>199</v>
       </c>
-      <c r="F122" s="5">
+      <c r="F122">
         <v>35</v>
       </c>
     </row>
@@ -3707,7 +3720,7 @@
       <c r="E123" t="s">
         <v>199</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123">
         <v>35</v>
       </c>
     </row>
@@ -3724,7 +3737,7 @@
       <c r="E124" t="s">
         <v>199</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124">
         <v>35</v>
       </c>
     </row>
@@ -3741,7 +3754,7 @@
       <c r="E125" t="s">
         <v>199</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125">
         <v>35</v>
       </c>
     </row>
@@ -3758,7 +3771,7 @@
       <c r="E126" t="s">
         <v>199</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126">
         <v>35</v>
       </c>
     </row>
@@ -3775,7 +3788,7 @@
       <c r="E127" t="s">
         <v>199</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127">
         <v>35</v>
       </c>
     </row>
@@ -3792,7 +3805,7 @@
       <c r="E128" t="s">
         <v>199</v>
       </c>
-      <c r="F128" s="5">
+      <c r="F128">
         <v>35</v>
       </c>
     </row>
@@ -3809,7 +3822,7 @@
       <c r="E129" t="s">
         <v>199</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129">
         <v>35</v>
       </c>
     </row>
@@ -3826,7 +3839,7 @@
       <c r="E130" t="s">
         <v>199</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130">
         <v>35</v>
       </c>
     </row>
@@ -3843,7 +3856,7 @@
       <c r="E131" t="s">
         <v>199</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131">
         <v>35</v>
       </c>
     </row>
@@ -3860,7 +3873,7 @@
       <c r="E132" t="s">
         <v>199</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132">
         <v>35</v>
       </c>
     </row>
@@ -3877,7 +3890,7 @@
       <c r="E133" t="s">
         <v>199</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133">
         <v>35</v>
       </c>
     </row>
@@ -3894,7 +3907,7 @@
       <c r="E134" t="s">
         <v>199</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134">
         <v>35</v>
       </c>
     </row>
@@ -3911,7 +3924,7 @@
       <c r="E135" t="s">
         <v>199</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135">
         <v>35</v>
       </c>
     </row>
@@ -3928,7 +3941,7 @@
       <c r="E136" t="s">
         <v>199</v>
       </c>
-      <c r="F136" s="5">
+      <c r="F136">
         <v>35</v>
       </c>
     </row>
@@ -3945,7 +3958,7 @@
       <c r="E137" t="s">
         <v>199</v>
       </c>
-      <c r="F137" s="5">
+      <c r="F137">
         <v>35</v>
       </c>
     </row>
@@ -3962,7 +3975,7 @@
       <c r="E138" t="s">
         <v>199</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138">
         <v>35</v>
       </c>
     </row>
@@ -3979,7 +3992,7 @@
       <c r="E139" t="s">
         <v>199</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139">
         <v>35</v>
       </c>
     </row>
@@ -3996,7 +4009,7 @@
       <c r="E140" t="s">
         <v>199</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140">
         <v>35</v>
       </c>
     </row>
@@ -4013,7 +4026,7 @@
       <c r="E141" t="s">
         <v>199</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141">
         <v>35</v>
       </c>
     </row>
@@ -4030,7 +4043,7 @@
       <c r="E142" t="s">
         <v>199</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142">
         <v>35</v>
       </c>
     </row>
@@ -4047,7 +4060,7 @@
       <c r="E143" t="s">
         <v>199</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143">
         <v>35</v>
       </c>
     </row>
@@ -4064,7 +4077,7 @@
       <c r="E144" t="s">
         <v>199</v>
       </c>
-      <c r="F144" s="5">
+      <c r="F144">
         <v>35</v>
       </c>
     </row>
@@ -4081,7 +4094,7 @@
       <c r="E145" t="s">
         <v>199</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145">
         <v>35</v>
       </c>
     </row>
@@ -4098,7 +4111,7 @@
       <c r="E146" t="s">
         <v>199</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146">
         <v>35</v>
       </c>
     </row>
@@ -4115,7 +4128,7 @@
       <c r="E147" t="s">
         <v>199</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147">
         <v>35</v>
       </c>
     </row>
@@ -4132,7 +4145,7 @@
       <c r="E148" t="s">
         <v>199</v>
       </c>
-      <c r="F148" s="5">
+      <c r="F148">
         <v>35</v>
       </c>
     </row>
@@ -4149,7 +4162,7 @@
       <c r="E149" t="s">
         <v>199</v>
       </c>
-      <c r="F149" s="5">
+      <c r="F149">
         <v>35</v>
       </c>
     </row>
@@ -4166,7 +4179,7 @@
       <c r="E150" t="s">
         <v>199</v>
       </c>
-      <c r="F150" s="5">
+      <c r="F150">
         <v>35</v>
       </c>
     </row>
@@ -4183,7 +4196,7 @@
       <c r="E151" t="s">
         <v>199</v>
       </c>
-      <c r="F151" s="5">
+      <c r="F151">
         <v>35</v>
       </c>
     </row>
@@ -4200,7 +4213,7 @@
       <c r="E152" t="s">
         <v>199</v>
       </c>
-      <c r="F152" s="5">
+      <c r="F152">
         <v>35</v>
       </c>
     </row>
@@ -4217,7 +4230,7 @@
       <c r="E153" t="s">
         <v>199</v>
       </c>
-      <c r="F153" s="5">
+      <c r="F153">
         <v>35</v>
       </c>
     </row>
@@ -4234,7 +4247,7 @@
       <c r="E154" t="s">
         <v>199</v>
       </c>
-      <c r="F154" s="5">
+      <c r="F154">
         <v>35</v>
       </c>
     </row>
@@ -4251,7 +4264,7 @@
       <c r="E155" t="s">
         <v>199</v>
       </c>
-      <c r="F155" s="5">
+      <c r="F155">
         <v>35</v>
       </c>
     </row>
@@ -4268,7 +4281,7 @@
       <c r="E156" t="s">
         <v>199</v>
       </c>
-      <c r="F156" s="5">
+      <c r="F156">
         <v>35</v>
       </c>
     </row>
@@ -4285,7 +4298,7 @@
       <c r="E157" t="s">
         <v>199</v>
       </c>
-      <c r="F157" s="5">
+      <c r="F157">
         <v>35</v>
       </c>
     </row>
@@ -4302,7 +4315,7 @@
       <c r="E158" t="s">
         <v>199</v>
       </c>
-      <c r="F158" s="5">
+      <c r="F158">
         <v>35</v>
       </c>
     </row>
@@ -4319,7 +4332,7 @@
       <c r="E159" t="s">
         <v>199</v>
       </c>
-      <c r="F159" s="5">
+      <c r="F159">
         <v>35</v>
       </c>
     </row>
@@ -4336,7 +4349,7 @@
       <c r="E160" t="s">
         <v>199</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160">
         <v>35</v>
       </c>
     </row>
@@ -4353,7 +4366,7 @@
       <c r="E161" t="s">
         <v>199</v>
       </c>
-      <c r="F161" s="5">
+      <c r="F161">
         <v>35</v>
       </c>
     </row>
@@ -4370,7 +4383,7 @@
       <c r="E162" t="s">
         <v>199</v>
       </c>
-      <c r="F162" s="5">
+      <c r="F162">
         <v>35</v>
       </c>
     </row>
@@ -4387,7 +4400,7 @@
       <c r="E163" t="s">
         <v>199</v>
       </c>
-      <c r="F163" s="5">
+      <c r="F163">
         <v>35</v>
       </c>
     </row>
@@ -4404,7 +4417,7 @@
       <c r="E164" t="s">
         <v>199</v>
       </c>
-      <c r="F164" s="5">
+      <c r="F164">
         <v>35</v>
       </c>
     </row>
@@ -4421,7 +4434,7 @@
       <c r="E165" t="s">
         <v>199</v>
       </c>
-      <c r="F165" s="5">
+      <c r="F165">
         <v>35</v>
       </c>
     </row>
@@ -4438,7 +4451,7 @@
       <c r="E166" t="s">
         <v>199</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166">
         <v>35</v>
       </c>
     </row>
@@ -4455,7 +4468,7 @@
       <c r="E167" t="s">
         <v>199</v>
       </c>
-      <c r="F167" s="5">
+      <c r="F167">
         <v>35</v>
       </c>
     </row>
@@ -4472,7 +4485,7 @@
       <c r="E168" t="s">
         <v>199</v>
       </c>
-      <c r="F168" s="5">
+      <c r="F168">
         <v>35</v>
       </c>
     </row>
@@ -4489,7 +4502,7 @@
       <c r="E169" t="s">
         <v>199</v>
       </c>
-      <c r="F169" s="5">
+      <c r="F169">
         <v>35</v>
       </c>
     </row>
@@ -4506,7 +4519,7 @@
       <c r="E170" t="s">
         <v>199</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170">
         <v>35</v>
       </c>
     </row>
@@ -4523,7 +4536,7 @@
       <c r="E171" t="s">
         <v>199</v>
       </c>
-      <c r="F171" s="5">
+      <c r="F171">
         <v>35</v>
       </c>
     </row>
@@ -4540,7 +4553,7 @@
       <c r="E172" t="s">
         <v>199</v>
       </c>
-      <c r="F172" s="5">
+      <c r="F172">
         <v>35</v>
       </c>
     </row>
@@ -4557,7 +4570,7 @@
       <c r="E173" t="s">
         <v>199</v>
       </c>
-      <c r="F173" s="5">
+      <c r="F173">
         <v>35</v>
       </c>
     </row>
@@ -4574,7 +4587,7 @@
       <c r="E174" t="s">
         <v>199</v>
       </c>
-      <c r="F174" s="5">
+      <c r="F174">
         <v>35</v>
       </c>
     </row>
@@ -4591,7 +4604,7 @@
       <c r="E175" t="s">
         <v>199</v>
       </c>
-      <c r="F175" s="5">
+      <c r="F175">
         <v>35</v>
       </c>
     </row>
@@ -4608,7 +4621,7 @@
       <c r="E176" t="s">
         <v>199</v>
       </c>
-      <c r="F176" s="5">
+      <c r="F176">
         <v>35</v>
       </c>
     </row>
@@ -4625,7 +4638,7 @@
       <c r="E177" t="s">
         <v>199</v>
       </c>
-      <c r="F177" s="5">
+      <c r="F177">
         <v>35</v>
       </c>
     </row>
@@ -4642,7 +4655,7 @@
       <c r="E178" t="s">
         <v>199</v>
       </c>
-      <c r="F178" s="5">
+      <c r="F178">
         <v>35</v>
       </c>
     </row>
@@ -4659,7 +4672,7 @@
       <c r="E179" t="s">
         <v>199</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179">
         <v>35</v>
       </c>
     </row>
@@ -4676,7 +4689,7 @@
       <c r="E180" t="s">
         <v>199</v>
       </c>
-      <c r="F180" s="5">
+      <c r="F180">
         <v>35</v>
       </c>
     </row>
@@ -4693,7 +4706,7 @@
       <c r="E181" t="s">
         <v>199</v>
       </c>
-      <c r="F181" s="5">
+      <c r="F181">
         <v>35</v>
       </c>
     </row>
@@ -4710,7 +4723,7 @@
       <c r="E182" t="s">
         <v>199</v>
       </c>
-      <c r="F182" s="5">
+      <c r="F182">
         <v>35</v>
       </c>
     </row>
@@ -4727,7 +4740,7 @@
       <c r="E183" t="s">
         <v>199</v>
       </c>
-      <c r="F183" s="5">
+      <c r="F183">
         <v>35</v>
       </c>
     </row>
@@ -4744,7 +4757,7 @@
       <c r="E184" t="s">
         <v>199</v>
       </c>
-      <c r="F184" s="5">
+      <c r="F184">
         <v>35</v>
       </c>
     </row>
@@ -4761,7 +4774,7 @@
       <c r="E185" t="s">
         <v>199</v>
       </c>
-      <c r="F185" s="5">
+      <c r="F185">
         <v>35</v>
       </c>
     </row>
@@ -4778,7 +4791,7 @@
       <c r="E186" t="s">
         <v>199</v>
       </c>
-      <c r="F186" s="5">
+      <c r="F186">
         <v>35</v>
       </c>
     </row>
@@ -4795,7 +4808,7 @@
       <c r="E187" t="s">
         <v>199</v>
       </c>
-      <c r="F187" s="5">
+      <c r="F187">
         <v>35</v>
       </c>
     </row>
@@ -4812,7 +4825,7 @@
       <c r="E188" t="s">
         <v>199</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F188">
         <v>35</v>
       </c>
     </row>
@@ -4829,7 +4842,7 @@
       <c r="E189" t="s">
         <v>199</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189">
         <v>35</v>
       </c>
     </row>
@@ -4846,7 +4859,7 @@
       <c r="E190" t="s">
         <v>199</v>
       </c>
-      <c r="F190" s="5">
+      <c r="F190">
         <v>35</v>
       </c>
     </row>
@@ -4863,7 +4876,7 @@
       <c r="E191" t="s">
         <v>199</v>
       </c>
-      <c r="F191" s="5">
+      <c r="F191">
         <v>35</v>
       </c>
     </row>
@@ -4880,7 +4893,7 @@
       <c r="E192" t="s">
         <v>199</v>
       </c>
-      <c r="F192" s="5">
+      <c r="F192">
         <v>35</v>
       </c>
     </row>
@@ -4897,7 +4910,7 @@
       <c r="E193" t="s">
         <v>199</v>
       </c>
-      <c r="F193" s="5">
+      <c r="F193">
         <v>35</v>
       </c>
     </row>
@@ -4914,7 +4927,7 @@
       <c r="E194" t="s">
         <v>199</v>
       </c>
-      <c r="F194" s="5">
+      <c r="F194">
         <v>35</v>
       </c>
     </row>
@@ -4931,7 +4944,7 @@
       <c r="E195" t="s">
         <v>199</v>
       </c>
-      <c r="F195" s="5">
+      <c r="F195">
         <v>35</v>
       </c>
     </row>
@@ -4948,7 +4961,7 @@
       <c r="E196" t="s">
         <v>199</v>
       </c>
-      <c r="F196" s="5">
+      <c r="F196">
         <v>35</v>
       </c>
     </row>
@@ -4965,7 +4978,7 @@
       <c r="E197" t="s">
         <v>199</v>
       </c>
-      <c r="F197" s="5">
+      <c r="F197">
         <v>35</v>
       </c>
     </row>
@@ -4982,7 +4995,7 @@
       <c r="E198" t="s">
         <v>199</v>
       </c>
-      <c r="F198" s="5">
+      <c r="F198">
         <v>35</v>
       </c>
     </row>
@@ -4999,7 +5012,7 @@
       <c r="E199" t="s">
         <v>199</v>
       </c>
-      <c r="F199" s="5">
+      <c r="F199">
         <v>35</v>
       </c>
     </row>
@@ -5016,7 +5029,7 @@
       <c r="E200" t="s">
         <v>199</v>
       </c>
-      <c r="F200" s="5">
+      <c r="F200">
         <v>35</v>
       </c>
     </row>
@@ -5033,7 +5046,7 @@
       <c r="E201" t="s">
         <v>199</v>
       </c>
-      <c r="F201" s="5">
+      <c r="F201">
         <v>35</v>
       </c>
     </row>
@@ -5050,7 +5063,7 @@
       <c r="E202" t="s">
         <v>199</v>
       </c>
-      <c r="F202" s="5">
+      <c r="F202">
         <v>35</v>
       </c>
     </row>
@@ -5067,7 +5080,7 @@
       <c r="E203" t="s">
         <v>199</v>
       </c>
-      <c r="F203" s="5">
+      <c r="F203">
         <v>35</v>
       </c>
     </row>
@@ -5084,7 +5097,7 @@
       <c r="E204" t="s">
         <v>199</v>
       </c>
-      <c r="F204" s="5">
+      <c r="F204">
         <v>35</v>
       </c>
     </row>
@@ -5101,7 +5114,7 @@
       <c r="E205" t="s">
         <v>199</v>
       </c>
-      <c r="F205" s="5">
+      <c r="F205">
         <v>35</v>
       </c>
     </row>
@@ -5118,7 +5131,7 @@
       <c r="E206" t="s">
         <v>199</v>
       </c>
-      <c r="F206" s="5">
+      <c r="F206">
         <v>35</v>
       </c>
     </row>
@@ -5135,7 +5148,7 @@
       <c r="E207" t="s">
         <v>199</v>
       </c>
-      <c r="F207" s="5">
+      <c r="F207">
         <v>35</v>
       </c>
     </row>
@@ -5152,7 +5165,7 @@
       <c r="E208" t="s">
         <v>199</v>
       </c>
-      <c r="F208" s="5">
+      <c r="F208">
         <v>35</v>
       </c>
     </row>
@@ -5169,7 +5182,7 @@
       <c r="E209" t="s">
         <v>199</v>
       </c>
-      <c r="F209" s="5">
+      <c r="F209">
         <v>35</v>
       </c>
     </row>
@@ -5186,7 +5199,7 @@
       <c r="E210" t="s">
         <v>199</v>
       </c>
-      <c r="F210" s="5">
+      <c r="F210">
         <v>35</v>
       </c>
     </row>
@@ -5203,7 +5216,7 @@
       <c r="E211" t="s">
         <v>199</v>
       </c>
-      <c r="F211" s="5">
+      <c r="F211">
         <v>35</v>
       </c>
     </row>
@@ -5220,7 +5233,7 @@
       <c r="E212" t="s">
         <v>199</v>
       </c>
-      <c r="F212" s="5">
+      <c r="F212">
         <v>35</v>
       </c>
     </row>
@@ -5237,7 +5250,7 @@
       <c r="E213" t="s">
         <v>199</v>
       </c>
-      <c r="F213" s="5">
+      <c r="F213">
         <v>35</v>
       </c>
     </row>
@@ -5254,7 +5267,7 @@
       <c r="E214" t="s">
         <v>199</v>
       </c>
-      <c r="F214" s="5">
+      <c r="F214">
         <v>35</v>
       </c>
     </row>
@@ -5271,7 +5284,7 @@
       <c r="E215" t="s">
         <v>199</v>
       </c>
-      <c r="F215" s="5">
+      <c r="F215">
         <v>35</v>
       </c>
     </row>
@@ -5288,7 +5301,7 @@
       <c r="E216" t="s">
         <v>199</v>
       </c>
-      <c r="F216" s="5">
+      <c r="F216">
         <v>35</v>
       </c>
     </row>
@@ -5305,7 +5318,7 @@
       <c r="E217" t="s">
         <v>199</v>
       </c>
-      <c r="F217" s="5">
+      <c r="F217">
         <v>35</v>
       </c>
     </row>
@@ -5322,7 +5335,7 @@
       <c r="E218" t="s">
         <v>199</v>
       </c>
-      <c r="F218" s="5">
+      <c r="F218">
         <v>35</v>
       </c>
     </row>
@@ -5339,7 +5352,7 @@
       <c r="E219" t="s">
         <v>199</v>
       </c>
-      <c r="F219" s="5">
+      <c r="F219">
         <v>35</v>
       </c>
     </row>
@@ -5356,7 +5369,7 @@
       <c r="E220" t="s">
         <v>199</v>
       </c>
-      <c r="F220" s="5">
+      <c r="F220">
         <v>35</v>
       </c>
     </row>
@@ -5373,7 +5386,7 @@
       <c r="E221" t="s">
         <v>199</v>
       </c>
-      <c r="F221" s="5">
+      <c r="F221">
         <v>35</v>
       </c>
     </row>
@@ -5390,7 +5403,7 @@
       <c r="E222" t="s">
         <v>199</v>
       </c>
-      <c r="F222" s="5">
+      <c r="F222">
         <v>35</v>
       </c>
     </row>
@@ -5407,7 +5420,7 @@
       <c r="E223" t="s">
         <v>199</v>
       </c>
-      <c r="F223" s="5">
+      <c r="F223">
         <v>35</v>
       </c>
     </row>
@@ -9187,7 +9200,7 @@
       <c r="C252" t="s">
         <v>119</v>
       </c>
-      <c r="G252" s="5" t="s">
+      <c r="G252" t="s">
         <v>115</v>
       </c>
     </row>
@@ -9201,7 +9214,7 @@
       <c r="C253" t="s">
         <v>135</v>
       </c>
-      <c r="G253" s="5" t="s">
+      <c r="G253" t="s">
         <v>116</v>
       </c>
     </row>
@@ -9215,7 +9228,7 @@
       <c r="C254" t="s">
         <v>123</v>
       </c>
-      <c r="G254" s="5" t="s">
+      <c r="G254" t="s">
         <v>120</v>
       </c>
     </row>
@@ -9229,7 +9242,7 @@
       <c r="C255" t="s">
         <v>124</v>
       </c>
-      <c r="G255" s="5" t="s">
+      <c r="G255" t="s">
         <v>121</v>
       </c>
     </row>
@@ -9243,7 +9256,7 @@
       <c r="C256" t="s">
         <v>136</v>
       </c>
-      <c r="G256" s="5" t="s">
+      <c r="G256" t="s">
         <v>122</v>
       </c>
     </row>
@@ -9524,7 +9537,7 @@
       <c r="C272" t="s">
         <v>133</v>
       </c>
-      <c r="E272" s="5" t="s">
+      <c r="E272" t="s">
         <v>139</v>
       </c>
       <c r="F272" t="s">
@@ -9544,7 +9557,7 @@
       <c r="C273" t="s">
         <v>134</v>
       </c>
-      <c r="E273" s="5" t="s">
+      <c r="E273" t="s">
         <v>126</v>
       </c>
       <c r="F273" t="s">
@@ -9564,7 +9577,7 @@
       <c r="C274" t="s">
         <v>117</v>
       </c>
-      <c r="E274" s="5" t="s">
+      <c r="E274" t="s">
         <v>108</v>
       </c>
       <c r="F274" t="s">
@@ -9584,7 +9597,7 @@
       <c r="C275" t="s">
         <v>118</v>
       </c>
-      <c r="E275" s="5" t="s">
+      <c r="E275" t="s">
         <v>113</v>
       </c>
       <c r="F275" t="s">
@@ -9604,7 +9617,7 @@
       <c r="C276" t="s">
         <v>119</v>
       </c>
-      <c r="E276" s="5" t="s">
+      <c r="E276" t="s">
         <v>127</v>
       </c>
       <c r="F276" t="s">
@@ -9624,7 +9637,7 @@
       <c r="C277" t="s">
         <v>135</v>
       </c>
-      <c r="E277" s="5" t="s">
+      <c r="E277" t="s">
         <v>139</v>
       </c>
       <c r="F277" t="s">
@@ -9644,7 +9657,7 @@
       <c r="C278" t="s">
         <v>123</v>
       </c>
-      <c r="E278" s="5" t="s">
+      <c r="E278" t="s">
         <v>108</v>
       </c>
       <c r="F278" t="s">
@@ -9664,7 +9677,7 @@
       <c r="C279" t="s">
         <v>124</v>
       </c>
-      <c r="E279" s="5" t="s">
+      <c r="E279" t="s">
         <v>109</v>
       </c>
       <c r="F279" t="s">
@@ -9684,7 +9697,7 @@
       <c r="C280" t="s">
         <v>136</v>
       </c>
-      <c r="E280" s="5" t="s">
+      <c r="E280" t="s">
         <v>128</v>
       </c>
       <c r="F280" t="s">
@@ -9704,7 +9717,7 @@
       <c r="C281" t="s">
         <v>137</v>
       </c>
-      <c r="E281" s="5" t="s">
+      <c r="E281" t="s">
         <v>114</v>
       </c>
       <c r="F281" t="s">
@@ -9724,7 +9737,7 @@
       <c r="C282" t="s">
         <v>138</v>
       </c>
-      <c r="E282" s="5" t="s">
+      <c r="E282" t="s">
         <v>129</v>
       </c>
       <c r="F282" t="s">
@@ -9744,7 +9757,7 @@
       <c r="C283" t="s">
         <v>126</v>
       </c>
-      <c r="E283" s="5" t="s">
+      <c r="E283" t="s">
         <v>130</v>
       </c>
       <c r="G283" t="s">
@@ -12360,7 +12373,7 @@
       <c r="C9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="1">
         <v>0.12708333333333333</v>
       </c>
       <c r="E9" t="s">
@@ -12402,7 +12415,7 @@
       <c r="C12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="1">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E12" t="s">
@@ -12416,7 +12429,7 @@
       <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="1">
         <v>8.4722222222222227E-2</v>
       </c>
       <c r="E13" t="s">
@@ -12775,4 +12788,458 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E84D665-A756-46A2-888F-909553A5E225}">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/新建 Microsoft Excel 工作表.xlsx
+++ b/data/新建 Microsoft Excel 工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\2025\2025 leybold 图论\lbgraph\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1276F4D7-E407-45C0-B780-BD513535B45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78152D2-E31A-470F-9B19-1E7B735FB768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10600" yWindow="1240" windowWidth="20980" windowHeight="9320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
